--- a/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Schedule!$A:$G,Schedule!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1290,7 +1290,7 @@
         </row>
         <row r="6">
           <cell r="L6">
-            <v>45748</v>
+            <v>44013</v>
           </cell>
         </row>
         <row r="7">
@@ -1298,7 +1298,7 @@
             <v>100</v>
           </cell>
           <cell r="N7">
-            <v>46477</v>
+            <v>44377</v>
           </cell>
         </row>
         <row r="11">
@@ -1309,7 +1309,7 @@
             <v>3000</v>
           </cell>
           <cell r="N11">
-            <v>46112</v>
+            <v>44377</v>
           </cell>
         </row>
       </sheetData>
@@ -1986,7 +1986,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K8" s="7" t="str">
-        <f>IF(E8&gt;0,E8-J8," ")</f>
+        <f>IF(E8&gt;0,IF(V8&gt;0,0,E8-J8)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L8" s="7"/>
@@ -2036,7 +2036,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K9" s="7" t="str">
-        <f>IF(E9&gt;0,E9-J9," ")</f>
+        <f>IF(E9&gt;0,IF(V9&gt;0,0,E9-J9)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L9" s="7"/>
@@ -2086,7 +2086,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K10" s="7" t="str">
-        <f>IF(E10&gt;0,E10-J10," ")</f>
+        <f>IF(E10&gt;0,IF(V10&gt;0,0,E10-J10)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L10" s="7"/>
@@ -2275,7 +2275,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K14" s="7" t="str">
-        <f t="shared" ref="K14:K21" si="4">IF(E14&gt;0,E14-J14," ")</f>
+        <f t="shared" ref="K14:K21" si="4">IF(E14&gt;0,IF(V14&gt;0,0,E14-J14)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L14" s="7"/>
@@ -2910,7 +2910,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K25" s="7" t="str">
-        <f>IF(E25&gt;0,E25-J25," ")</f>
+        <f>IF(E25&gt;0,IF(V25&gt;0,0,E25-J25)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L25" s="7"/>
@@ -2972,7 +2972,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K26" s="7" t="str">
-        <f>IF(E26&gt;0,E26-J26," ")</f>
+        <f>IF(E26&gt;0,IF(V26&gt;0,0,E26-J26)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L26" s="7"/>
@@ -3034,7 +3034,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K27" s="7" t="str">
-        <f>IF(E27&gt;0,E27-J27," ")</f>
+        <f>IF(E27&gt;0,IF(V27&gt;0,0,E27-J27)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L27" s="7"/>
@@ -3096,7 +3096,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K28" s="7" t="str">
-        <f>IF(E28&gt;0,E28-J28," ")</f>
+        <f>IF(E28&gt;0,IF(V28&gt;0,0,E28-J28)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L28" s="7"/>
@@ -3158,7 +3158,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K29" s="7" t="str">
-        <f>IF(E29&gt;0,E29-J29," ")</f>
+        <f>IF(E29&gt;0,IF(V29&gt;0,0,E29-J29)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L29" s="7"/>
@@ -3359,7 +3359,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K33" s="7" t="str">
-        <f t="shared" ref="K33:K40" si="15">IF(E33&gt;0,E33-J33," ")</f>
+        <f t="shared" ref="K33:K40" si="15">IF(E33&gt;0,IF(V33&gt;0,0,E33-J33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L33" s="7"/>
@@ -3994,7 +3994,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K44" s="7" t="str">
-        <f t="shared" ref="K44:K54" si="26">IF(E44&gt;0,E44-J44," ")</f>
+        <f t="shared" ref="K44:K54" si="26">IF(E44&gt;0,IF(V44&gt;0,0,E44-J44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L44" s="7"/>
@@ -4122,7 +4122,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K46" s="7" t="str">
-        <f>IF(E46&gt;0,E46-J46," ")</f>
+        <f>IF(E46&gt;0,IF(V46&gt;0,0,E46-J46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L46" s="7"/>
@@ -4186,7 +4186,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K47" s="7" t="str">
-        <f>IF(E47&gt;0,E47-J47," ")</f>
+        <f>IF(E47&gt;0,IF(V47&gt;0,0,E47-J47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L47" s="7"/>
@@ -4250,7 +4250,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K48" s="7" t="str">
-        <f>IF(E48&gt;0,E48-J48," ")</f>
+        <f>IF(E48&gt;0,IF(V48&gt;0,0,E48-J48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L48" s="7"/>
@@ -4950,7 +4950,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K61" s="7" t="str">
-        <f>IF(E61&gt;0,E61-J61," ")</f>
+        <f>IF(E61&gt;0,IF(V61&gt;0,0,E61-J61)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L61" s="7"/>
@@ -4997,7 +4997,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K62" s="7" t="str">
-        <f>IF(E62&gt;0,E62-J62," ")</f>
+        <f>IF(E62&gt;0,IF(V62&gt;0,0,E62-J62)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L62" s="7"/>
@@ -5044,7 +5044,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K63" s="7" t="str">
-        <f>IF(E63&gt;0,E63-J63," ")</f>
+        <f>IF(E63&gt;0,IF(V63&gt;0,0,E63-J63)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L63" s="7"/>
@@ -5230,7 +5230,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K67" s="7" t="str">
-        <f t="shared" ref="K67:K74" si="35">IF(E67&gt;0,E67-J67," ")</f>
+        <f t="shared" ref="K67:K74" si="35">IF(E67&gt;0,IF(V67&gt;0,0,E67-J67)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L67" s="7"/>
@@ -5865,7 +5865,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K78" s="7" t="str">
-        <f>IF(E78&gt;0,E78-J78," ")</f>
+        <f>IF(E78&gt;0,IF(V78&gt;0,0,E78-J78)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L78" s="7"/>
@@ -5927,7 +5927,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K79" s="7" t="str">
-        <f>IF(E79&gt;0,E79-J79," ")</f>
+        <f>IF(E79&gt;0,IF(V79&gt;0,0,E79-J79)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L79" s="7"/>
@@ -5989,7 +5989,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K80" s="7" t="str">
-        <f>IF(E80&gt;0,E80-J80," ")</f>
+        <f>IF(E80&gt;0,IF(V80&gt;0,0,E80-J80)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L80" s="7"/>
@@ -6051,7 +6051,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K81" s="7" t="str">
-        <f>IF(E81&gt;0,E81-J81," ")</f>
+        <f>IF(E81&gt;0,IF(V81&gt;0,0,E81-J81)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L81" s="7"/>
@@ -6113,7 +6113,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K82" s="7" t="str">
-        <f>IF(E82&gt;0,E82-J82," ")</f>
+        <f>IF(E82&gt;0,IF(V82&gt;0,0,E82-J82)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L82" s="7"/>
@@ -6314,7 +6314,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K86" s="7" t="str">
-        <f t="shared" ref="K86:K93" si="45">IF(E86&gt;0,E86-J86," ")</f>
+        <f t="shared" ref="K86:K93" si="45">IF(E86&gt;0,IF(V86&gt;0,0,E86-J86)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L86" s="7"/>
@@ -6949,7 +6949,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K97" s="7" t="str">
-        <f t="shared" ref="K97:K107" si="55">IF(E97&gt;0,E97-J97," ")</f>
+        <f t="shared" ref="K97:K107" si="55">IF(E97&gt;0,IF(V97&gt;0,0,E97-J97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L97" s="7"/>
@@ -7071,7 +7071,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K99" s="7" t="str">
-        <f>IF(E99&gt;0,E99-J99," ")</f>
+        <f>IF(E99&gt;0,IF(V99&gt;0,0,E99-J99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L99" s="7"/>
@@ -7132,7 +7132,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K100" s="7" t="str">
-        <f>IF(E100&gt;0,E100-J100," ")</f>
+        <f>IF(E100&gt;0,IF(V100&gt;0,0,E100-J100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L100" s="7"/>
@@ -7193,7 +7193,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K101" s="7" t="str">
-        <f>IF(E101&gt;0,E101-J101," ")</f>
+        <f>IF(E101&gt;0,IF(V101&gt;0,0,E101-J101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L101" s="7"/>
@@ -8648,7 +8648,7 @@
       <c r="G10" s="83"/>
       <c r="H10" s="89"/>
       <c r="I10" s="81" t="str">
-        <f>IF(H10&gt;0,#REF!/H10," ")</f>
+        <f>IF(E10&gt;0,(E10+F10+G10)/H10," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J10" s="81" t="str">
@@ -8687,7 +8687,7 @@
       <c r="G12" s="83"/>
       <c r="H12" s="89"/>
       <c r="I12" s="81" t="str">
-        <f>IF(H12&gt;0,#REF!/H12," ")</f>
+        <f>IF(E12&gt;0,(E12+F12+G12)/H12," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J12" s="81" t="str">
@@ -8726,7 +8726,7 @@
       <c r="G14" s="83"/>
       <c r="H14" s="89"/>
       <c r="I14" s="81" t="str">
-        <f>IF(H14&gt;0,#REF!/H14," ")</f>
+        <f>IF(E14&gt;0,(E14+F14+G14)/H14," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J14" s="81" t="str">
@@ -8765,7 +8765,7 @@
       <c r="G16" s="83"/>
       <c r="H16" s="89"/>
       <c r="I16" s="81" t="str">
-        <f>IF(H16&gt;0,#REF!/H16," ")</f>
+        <f>IF(E16&gt;0,(E16+F16+G16)/H16," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J16" s="81" t="str">
@@ -8804,7 +8804,7 @@
       <c r="G18" s="83"/>
       <c r="H18" s="89"/>
       <c r="I18" s="81" t="str">
-        <f>IF(H18&gt;0,#REF!/H18," ")</f>
+        <f>IF(E18&gt;0,(E18+F18+G18)/H18," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J18" s="81" t="str">
@@ -8843,7 +8843,7 @@
       <c r="G20" s="83"/>
       <c r="H20" s="89"/>
       <c r="I20" s="81" t="str">
-        <f>IF(H20&gt;0,#REF!/H20," ")</f>
+        <f>IF(E20&gt;0,(E20+F20+G20)/H20," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J20" s="81" t="str">
@@ -8882,7 +8882,7 @@
       <c r="G22" s="83"/>
       <c r="H22" s="89"/>
       <c r="I22" s="81" t="str">
-        <f>IF(H22&gt;0,#REF!/H22," ")</f>
+        <f>IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J22" s="81" t="str">
@@ -8921,7 +8921,7 @@
       <c r="G24" s="83"/>
       <c r="H24" s="89"/>
       <c r="I24" s="81" t="str">
-        <f>IF(H24&gt;0,#REF!/H24," ")</f>
+        <f>IF(E24&gt;0,(E24+F24+G24)/H24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J24" s="81" t="str">
@@ -8960,7 +8960,7 @@
       <c r="G26" s="83"/>
       <c r="H26" s="89"/>
       <c r="I26" s="81" t="str">
-        <f>IF(H26&gt;0,#REF!/H26," ")</f>
+        <f>IF(E26&gt;0,(E26+F26+G26)/H26," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J26" s="81" t="str">
@@ -9156,7 +9156,7 @@
       <c r="G36" s="83"/>
       <c r="H36" s="89"/>
       <c r="I36" s="81" t="str">
-        <f>IF(H36&gt;0,#REF!/H36," ")</f>
+        <f>IF(E36&gt;0,(E36+F36+G36)/H36," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J36" s="81" t="str">
@@ -9195,7 +9195,7 @@
       <c r="G38" s="83"/>
       <c r="H38" s="89"/>
       <c r="I38" s="81" t="str">
-        <f>IF(H38&gt;0,#REF!/H38," ")</f>
+        <f>IF(E38&gt;0,(E38+F38+G38)/H38," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J38" s="81" t="str">
@@ -9234,7 +9234,7 @@
       <c r="G40" s="83"/>
       <c r="H40" s="89"/>
       <c r="I40" s="81" t="str">
-        <f>IF(H40&gt;0,#REF!/H40," ")</f>
+        <f>IF(E40&gt;0,(E40+F40+G40)/H40," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J40" s="81" t="str">
@@ -9273,7 +9273,7 @@
       <c r="G42" s="83"/>
       <c r="H42" s="89"/>
       <c r="I42" s="81" t="str">
-        <f>IF(H42&gt;0,#REF!/H42," ")</f>
+        <f>IF(E42&gt;0,(E42+F42+G42)/H42," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J42" s="81" t="str">
@@ -9312,7 +9312,7 @@
       <c r="G44" s="83"/>
       <c r="H44" s="89"/>
       <c r="I44" s="81" t="str">
-        <f>IF(H44&gt;0,#REF!/H44," ")</f>
+        <f>IF(E44&gt;0,(E44+F44+G44)/H44," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J44" s="81" t="str">
@@ -9351,7 +9351,7 @@
       <c r="G46" s="83"/>
       <c r="H46" s="89"/>
       <c r="I46" s="81" t="str">
-        <f>IF(H46&gt;0,#REF!/H46," ")</f>
+        <f>IF(E46&gt;0,(E46+F46+G46)/H46," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J46" s="81" t="str">
@@ -9390,7 +9390,7 @@
       <c r="G48" s="83"/>
       <c r="H48" s="89"/>
       <c r="I48" s="81" t="str">
-        <f>IF(H48&gt;0,#REF!/H48," ")</f>
+        <f>IF(E48&gt;0,(E48+F48+G48)/H48," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J48" s="81" t="str">
@@ -9429,7 +9429,7 @@
       <c r="G50" s="83"/>
       <c r="H50" s="89"/>
       <c r="I50" s="81" t="str">
-        <f>IF(H50&gt;0,#REF!/H50," ")</f>
+        <f>IF(E50&gt;0,(E50+F50+G50)/H50," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J50" s="81" t="str">
@@ -9468,7 +9468,7 @@
       <c r="G52" s="83"/>
       <c r="H52" s="89"/>
       <c r="I52" s="81" t="str">
-        <f>IF(H52&gt;0,#REF!/H52," ")</f>
+        <f>IF(E52&gt;0,(E52+F52+G52)/H52," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J52" s="81" t="str">

--- a/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
@@ -1302,12 +1302,6 @@
           </cell>
         </row>
         <row r="11">
-          <cell r="E11">
-            <v>12000</v>
-          </cell>
-          <cell r="G11">
-            <v>3000</v>
-          </cell>
           <cell r="N11">
             <v>44377</v>
           </cell>
@@ -1851,7 +1845,8 @@
       </c>
       <c r="Q4" s="153"/>
       <c r="R4" s="118">
-        <v>20</v>
+        <f>[1]Admin!$G$6</f>
+        <v>18</v>
       </c>
       <c r="S4" s="110">
         <f>J4</f>
@@ -4006,7 +4001,7 @@
       <c r="P44" s="87"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11" t="str">
-        <f>IF(O44&gt;0,MIN(O44*R$4/100*(1-M44),3000*(1-M44))," ")</f>
+        <f>IF(O44&gt;0,O44*R$4/100*(1-M44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S44" s="11" t="str">
@@ -4070,7 +4065,7 @@
       <c r="P45" s="87"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11" t="str">
-        <f t="shared" ref="R45:R48" si="31">IF(O45&gt;0,MIN(O45*R$4/100*(1-M45),3000*(1-M45))," ")</f>
+        <f t="shared" ref="R45:R48" si="31">IF(O45&gt;0,O45*R$4/100*(1-M45)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S45" s="11" t="str">
@@ -4357,7 +4352,7 @@
       <c r="P50" s="87"/>
       <c r="Q50" s="11"/>
       <c r="R50" s="11" t="str">
-        <f>IF(O50&gt;0,IF(O50&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M50),O50*R$4/100)*(1-M50)," ")</f>
+        <f>IF(O50&gt;0,O50*R$4/100*(1-M50)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S50" s="11" t="str">
@@ -4421,7 +4416,7 @@
       <c r="P51" s="87"/>
       <c r="Q51" s="11"/>
       <c r="R51" s="11" t="str">
-        <f>IF(O51&gt;0,IF(O51&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M51),O51*R$4/100)*(1-M51)," ")</f>
+        <f>IF(O51&gt;0,O51*R$4/100*(1-M51)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S51" s="11" t="str">
@@ -4485,7 +4480,7 @@
       <c r="P52" s="87"/>
       <c r="Q52" s="11"/>
       <c r="R52" s="11" t="str">
-        <f>IF(O52&gt;0,IF(O52&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M52),O52*R$4/100)*(1-M52)," ")</f>
+        <f>IF(O52&gt;0,O52*R$4/100*(1-M52)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S52" s="11" t="str">
@@ -4549,7 +4544,7 @@
       <c r="P53" s="87"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="11" t="str">
-        <f>IF(O53&gt;0,IF(O53&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M53),O53*R$4/100)*(1-M53)," ")</f>
+        <f>IF(O53&gt;0,O53*R$4/100*(1-M53)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S53" s="11" t="str">
@@ -4613,7 +4608,7 @@
       <c r="P54" s="87"/>
       <c r="Q54" s="11"/>
       <c r="R54" s="11" t="str">
-        <f>IF(O54&gt;0,IF(O54&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M54),O54*R$4/100)*(1-M54)," ")</f>
+        <f>IF(O54&gt;0,O54*R$4/100*(1-M54)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S54" s="11" t="str">
@@ -6961,7 +6956,7 @@
       <c r="P97" s="87"/>
       <c r="Q97" s="11"/>
       <c r="R97" s="11" t="str">
-        <f>IF(E97&gt;0,IF(E97&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M97),E97*R$4/100)*(1-M97)," ")</f>
+        <f>IF(E97&gt;0,E97*R$4/100*(1-M97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S97" s="11" t="str">
@@ -7022,7 +7017,7 @@
       <c r="P98" s="87"/>
       <c r="Q98" s="11"/>
       <c r="R98" s="11" t="str">
-        <f>IF(E98&gt;0,IF(E98&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M98),E98*R$4/100)*(1-M98)," ")</f>
+        <f>IF(E98&gt;0,E98*R$4/100*(1-M98)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S98" s="11" t="str">
@@ -7083,7 +7078,7 @@
       <c r="P99" s="87"/>
       <c r="Q99" s="11"/>
       <c r="R99" s="11" t="str">
-        <f>IF(E99&gt;0,IF(E99&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M99),E99*R$4/100)*(1-M99)," ")</f>
+        <f>IF(E99&gt;0,E99*R$4/100*(1-M99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S99" s="11" t="str">
@@ -7144,7 +7139,7 @@
       <c r="P100" s="87"/>
       <c r="Q100" s="11"/>
       <c r="R100" s="11" t="str">
-        <f>IF(E100&gt;0,IF(E100&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M100),E100*R$4/100)*(1-M100)," ")</f>
+        <f>IF(E100&gt;0,E100*R$4/100*(1-M100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S100" s="11" t="str">
@@ -7205,7 +7200,7 @@
       <c r="P101" s="87"/>
       <c r="Q101" s="11"/>
       <c r="R101" s="11" t="str">
-        <f>IF(E101&gt;0,IF(E101&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M101),E101*R$4/100)*(1-M101)," ")</f>
+        <f>IF(E101&gt;0,E101*R$4/100*(1-M101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S101" s="11" t="str">

--- a/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Company 2021-06-30 (Jun21) Excel 2007/Fixedassets.xlsx
@@ -19,6 +19,8 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Schedule!$A:$G,Schedule!$1:$4</definedName>
@@ -1312,6 +1314,102 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="OpeningCreditors"/>
+      <sheetName val="Jul"/>
+      <sheetName val="Aug"/>
+      <sheetName val="Sep"/>
+      <sheetName val="Oct"/>
+      <sheetName val="Nov"/>
+      <sheetName val="Dec"/>
+      <sheetName val="Jan"/>
+      <sheetName val="Feb"/>
+      <sheetName val="Mar"/>
+      <sheetName val="Apr"/>
+      <sheetName val="May"/>
+      <sheetName val="Jun"/>
+      <sheetName val="ClosingCreditors"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="2">
+          <cell r="AI2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="OpeningDebtors"/>
+      <sheetName val="Jul"/>
+      <sheetName val="Aug"/>
+      <sheetName val="Sep"/>
+      <sheetName val="Oct"/>
+      <sheetName val="Nov"/>
+      <sheetName val="Dec"/>
+      <sheetName val="Jan"/>
+      <sheetName val="Feb"/>
+      <sheetName val="Mar"/>
+      <sheetName val="Apr"/>
+      <sheetName val="May"/>
+      <sheetName val="Jun"/>
+      <sheetName val="ClosingDebtors"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="2">
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -8284,9 +8382,9 @@
       </c>
       <c r="C13" s="178"/>
       <c r="D13" s="179"/>
-      <c r="E13" s="53" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="E13" s="53">
+        <f>[2]Jun!$AI$2</f>
+        <v>0</v>
       </c>
       <c r="F13" s="49"/>
       <c r="G13" s="172" t="s">
@@ -8295,9 +8393,9 @@
       <c r="H13" s="172"/>
       <c r="I13" s="172"/>
       <c r="J13" s="173"/>
-      <c r="K13" s="53" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="K13" s="53">
+        <f>[3]Jun!$U$2</f>
+        <v>0</v>
       </c>
       <c r="L13" s="49"/>
       <c r="M13" s="162"/>
@@ -8341,27 +8439,27 @@
     </row>
     <row r="15" spans="1:24" s="5" customFormat="1" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="63"/>
-      <c r="B15" s="169" t="e">
+      <c r="B15" s="169" t="str">
         <f>IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
-        <v>#REF!</v>
+        <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
       <c r="C15" s="170"/>
       <c r="D15" s="171"/>
-      <c r="E15" s="104" t="e">
+      <c r="E15" s="104">
         <f>E13-E11</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="F15" s="49"/>
-      <c r="G15" s="169" t="e">
+      <c r="G15" s="169" t="str">
         <f>IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
-        <v>#REF!</v>
+        <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
       <c r="H15" s="170"/>
       <c r="I15" s="170"/>
       <c r="J15" s="171"/>
-      <c r="K15" s="104" t="e">
+      <c r="K15" s="104">
         <f>K13-K11</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="L15" s="49"/>
       <c r="M15" s="162"/>
